--- a/artfynd/A 47888-2021 artfynd.xlsx
+++ b/artfynd/A 47888-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47888-2021 artfynd.xlsx
+++ b/artfynd/A 47888-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102075011</v>
+        <v>102075434</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>219795</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Höjden, Vrm</t>
+          <t>Östra Höjden , Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463705.8958351015</v>
+        <v>463668</v>
       </c>
       <c r="R2" t="n">
-        <v>6639153.730824187</v>
+        <v>6639186</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,12 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Många ex I kalkbarrskog</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,15 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102074925</v>
+        <v>102075454</v>
       </c>
       <c r="B3" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,24 +813,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -845,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463717.3063540446</v>
+        <v>463713</v>
       </c>
       <c r="R3" t="n">
-        <v>6639138.059321399</v>
+        <v>6639147</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,12 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Många ex I kalkbarrskog</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102075454</v>
+        <v>102074925</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,33 +936,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -978,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463712.8701957372</v>
+        <v>463717</v>
       </c>
       <c r="R4" t="n">
-        <v>6639147.137473729</v>
+        <v>6639139</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1007,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Många ex I kalkbarrskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,52 +1044,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102074980</v>
+        <v>102074890</v>
       </c>
       <c r="B5" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Höjden, Vrm</t>
+          <t>Östra Höjden , Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463710.8592683562</v>
+        <v>463714</v>
       </c>
       <c r="R5" t="n">
-        <v>6639147.157160787</v>
+        <v>6639134</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1139,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Många ex I kalkbarrskog</t>
+          <t>Många ex i kalkbarrskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1158,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,15 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102074890</v>
+        <v>102074980</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,49 +1187,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Höjden , Vrm</t>
+          <t>Östra Höjden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463714.250650808</v>
+        <v>463711</v>
       </c>
       <c r="R6" t="n">
-        <v>6639134.073792649</v>
+        <v>6639147</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1269,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1279,12 +1258,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Många ex i kalkbarrskog</t>
+          <t>Många ex I kalkbarrskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,7 +1277,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1316,15 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102075434</v>
+        <v>102075011</v>
       </c>
       <c r="B7" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,49 +1306,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219795</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östra Höjden , Vrm</t>
+          <t>Östra Höjden, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463667.5003988513</v>
+        <v>463706</v>
       </c>
       <c r="R7" t="n">
-        <v>6639186.230220526</v>
+        <v>6639154</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1406,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1416,7 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många ex I kalkbarrskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1451,12 +1421,7 @@
         <v>102075001</v>
       </c>
       <c r="B8" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,10 +1459,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463707.8920170177</v>
+        <v>463708</v>
       </c>
       <c r="R8" t="n">
-        <v>6639152.205495209</v>
+        <v>6639152</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 47888-2021 artfynd.xlsx
+++ b/artfynd/A 47888-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102075434</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102075454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074925</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1173,6 +1193,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074890</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1292,6 +1317,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074980</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1415,6 +1445,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102075011</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1538,8 +1573,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102075001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>